--- a/healthcare_surveys/029_mental_health_stigma_in_healthcare_settings_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/029_mental_health_stigma_in_healthcare_settings_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider</t>
+          <t>Do you feel comfortable talking about mental health topics?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How often have you experienced stigma from a healthcare provider</t>
+          <t>Do you feel comfortable sharing mental health information with healthcare providers?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often have you experienced stigma from a healthcare provider</t>
+          <t>How often do you feel comfortable sharing mental health information with healthcare providers?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How often have you experienced stigma from a healthcare provider</t>
+          <t>Do healthcare providers ask how you are doing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider at work</t>
+          <t>Do you feel comfortable telling healthcare providers if you are experiencing mental health issues?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>healthcare_surveys_survey_form_page_1_6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Have you experienced stigma from a healthcare provider at work</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often have you experienced stigma from a healthcare provider at work</t>
+          <t>How often do you feel comfortable telling healthcare providers about your mental health issues?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider at home</t>
+          <t>How often do you feel uncomfortable asking a healthcare provider about your mental health issues?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider at home</t>
+          <t>Do you feel uncomfortable telling healthcare providers about your mental health issues?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>healthcare_surveys_survey_form_page_1_10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>How often have you experienced stigma from a healthcare provider at home</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider in the community</t>
+          <t>Healthcare Surveys Survey Form Page 1 11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider in the community</t>
+          <t>How often do you feel uncomfortable sharing mental health information with healthcare providers?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider in public settings</t>
+          <t>Healthcare Surveys Survey Form Page 1 13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Have you experienced stigma from a healthcare provider in public settings</t>
+          <t>Do healthcare providers ask about your mental health?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Do you feel comfortable talking about mental health topics</t>
+          <t>Do you feel comfortable talking about mental health issues with healthcare providers?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you feel comfortable talking about mental health topics</t>
+          <t>Do you feel comfortable asking healthcare providers about your mental health issues?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Do you feel comfortable sharing mental health information with healthcare providers</t>
+          <t>Do you feel uncomfortable sharing mental health information with healthcare providers?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Do you feel comfortable sharing mental health information with healthcare providers</t>
+          <t>Healthcare Surveys Survey Form Page 1 18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How often do you share mental health information with healthcare providers</t>
+          <t>What are some of the reasons why you may not have shared mental health information with healthcare providers?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Do healthcare providers ask how you are doing</t>
+          <t>Do healthcare providers have a way to ask about your mental health issues?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Do healthcare providers ask how you are doing</t>
+          <t>Do you feel comfortable discussing mental health issues with healthcare providers?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How often do you feel comfortable telling healthcare providers if you are experiencing mental health issues</t>
+          <t>Do you feel comfortable talking about mental health topics with healthcare providers?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Do you feel comfortable telling healthcare providers about your mental health issues</t>
+          <t>Healthcare Surveys Survey Form Page 1 23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1077,11 +1077,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Do you feel uncomfortable asking a healthcare provider about your mental health issues</t>
+          <t>Healthcare Surveys Survey Form Page 1 24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>healthcare_surveys_survey_form_page_1_25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1182,726 +1205,726 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_6_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_6_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_8_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_8_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_8_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_8_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_9_choices</t>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_9_choices</t>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_11_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_11_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_11_choices</t>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_11_choices</t>
+          <t>do_you_feel_uncomfortable_asking_a_healthcare_provider_about_your_mental_health_issues_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_12_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_12_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_13_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_13_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_13_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_13_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_14_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_15_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_16_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_17_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_18_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_18_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_frequently'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, frequently'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_sometimes'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, sometimes'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_22_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_20_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_22_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_22_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_21_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_22_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
@@ -1930,46 +1953,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>yes,_sometimes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Yes, sometimes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_24_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_23_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>healthcare_surveys_survey_form_page_1_24_choices</t>
+          <t>healthcare_surveys_survey_form_page_1_23_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
